--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
   <si>
     <t/>
   </si>
   <si>
-    <t>20135312</t>
-  </si>
-  <si>
-    <t>WOW SPAGETI CB 80 G</t>
+    <t>10005073</t>
+  </si>
+  <si>
+    <t>BLUE BAND PCK 200 G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -31,58 +31,61 @@
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20135313</t>
-  </si>
-  <si>
-    <t>WOW SPAGETI BG 76 G</t>
+    <t>20069768</t>
+  </si>
+  <si>
+    <t>BIHUNKU STO SPS 55 G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20032723</t>
-  </si>
-  <si>
-    <t>MILO CEREAL CKT 30 G</t>
+    <t>20104077</t>
+  </si>
+  <si>
+    <t>SEDAP KCP SPCL 725 G</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>10025006</t>
-  </si>
-  <si>
-    <t>NESTLE KOKO CMB 30 G</t>
+    <t>10036685</t>
+  </si>
+  <si>
+    <t>NUTELLA J HZNT 200 G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>10003336</t>
-  </si>
-  <si>
-    <t>EMRON SH BK&amp;S 170 ML</t>
+    <t>20002944</t>
+  </si>
+  <si>
+    <t>PSODENT HERBAL 190 G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20039728</t>
-  </si>
-  <si>
-    <t>SHINZU'I KEI 380 ML</t>
+    <t>PT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20087203</t>
+  </si>
+  <si>
+    <t>CSSN BW BN P 3X45'S</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20130653</t>
-  </si>
-  <si>
-    <t>SHINZU'I SKRA 380 ML</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20009500</t>
+  </si>
+  <si>
+    <t>BIORE BF RELX 400 ML</t>
   </si>
   <si>
     <t>7</t>
@@ -91,37 +94,37 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20143339</t>
-  </si>
-  <si>
-    <t>LFBUOY BW L.FR 350 G</t>
+    <t>20021816</t>
+  </si>
+  <si>
+    <t>VSLNE LOT BRIGHT 200</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>PT,(E-27H)</t>
-  </si>
-  <si>
-    <t>20067449</t>
-  </si>
-  <si>
-    <t>GLW&amp;LV DRM.GL 100 G</t>
+    <t>PT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20110001</t>
+  </si>
+  <si>
+    <t>WRDH UV GRD GL 40 ML</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>PT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20133309</t>
-  </si>
-  <si>
-    <t>GLAD2 POMEGRNT 30 G</t>
+    <t>10002941</t>
+  </si>
+  <si>
+    <t>C.LANG KY PTH 120 ML</t>
   </si>
   <si>
     <t>10</t>
+  </si>
+  <si>
+    <t>RT,(E-6B)</t>
   </si>
 </sst>
 </file>
@@ -521,7 +524,7 @@
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="11" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -641,15 +644,15 @@
         <v>17</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>5</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -658,18 +661,18 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
@@ -678,18 +681,18 @@
         <v>4</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
@@ -698,18 +701,18 @@
         <v>4</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>3</v>
@@ -718,10 +721,10 @@
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -741,7 +744,7 @@
         <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>

--- a/E/DU4AMKT.xlsx
+++ b/E/DU4AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="41">
   <si>
     <t/>
   </si>
   <si>
-    <t>10005073</t>
-  </si>
-  <si>
-    <t>BLUE BAND PCK 200 G</t>
+    <t>10008819</t>
+  </si>
+  <si>
+    <t>BANGO KCAP MNS 700 G</t>
   </si>
   <si>
     <t>DU4AMKT</t>
@@ -28,64 +28,64 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-0.5B)</t>
+  </si>
+  <si>
+    <t>20036590</t>
+  </si>
+  <si>
+    <t>LUWAK WHT ORG 9x20 G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>10025006</t>
+  </si>
+  <si>
+    <t>NESTLE KOKO CMB 30 G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20069768</t>
-  </si>
-  <si>
-    <t>BIHUNKU STO SPS 55 G</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>20104077</t>
-  </si>
-  <si>
-    <t>SEDAP KCP SPCL 725 G</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>10036685</t>
-  </si>
-  <si>
-    <t>NUTELLA J HZNT 200 G</t>
+    <t>20032723</t>
+  </si>
+  <si>
+    <t>MILO CEREAL CKT 30 G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20002944</t>
-  </si>
-  <si>
-    <t>PSODENT HERBAL 190 G</t>
+    <t>20127600</t>
+  </si>
+  <si>
+    <t>CPTADEN J C.MT 225 G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20087203</t>
-  </si>
-  <si>
-    <t>CSSN BW BN P 3X45'S</t>
+    <t>20116823</t>
+  </si>
+  <si>
+    <t>CPTADEN J FRH 225 G</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20009500</t>
-  </si>
-  <si>
-    <t>BIORE BF RELX 400 ML</t>
+    <t>10012742</t>
+  </si>
+  <si>
+    <t>LSTERNE CLMIN 250 ML</t>
   </si>
   <si>
     <t>7</t>
@@ -94,37 +94,46 @@
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20021816</t>
-  </si>
-  <si>
-    <t>VSLNE LOT BRIGHT 200</t>
+    <t>20141370</t>
+  </si>
+  <si>
+    <t>LSTERNE WTRML 250 ML</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
-    <t>PT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20110001</t>
-  </si>
-  <si>
-    <t>WRDH UV GRD GL 40 ML</t>
+    <t>20067449</t>
+  </si>
+  <si>
+    <t>GLW&amp;LV DRM.GL 100 G</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
-    <t>10002941</t>
-  </si>
-  <si>
-    <t>C.LANG KY PTH 120 ML</t>
+    <t>PT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20137253</t>
+  </si>
+  <si>
+    <t>BRVEN EDP C/W 100 ML</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
-    <t>RT,(E-6B)</t>
+    <t>20139611</t>
+  </si>
+  <si>
+    <t>FRSH/C STRONG 15+5ML</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
   </si>
 </sst>
 </file>
@@ -517,14 +526,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="4" max="4" width="3" customWidth="1"/>
     <col min="5" max="5" width="4" customWidth="1"/>
-    <col min="6" max="6" width="11" customWidth="1"/>
+    <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -584,15 +593,15 @@
         <v>8</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
@@ -601,38 +610,38 @@
         <v>4</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
@@ -641,18 +650,18 @@
         <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
@@ -661,10 +670,10 @@
         <v>4</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -704,27 +713,27 @@
         <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E10" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="E10" s="1" t="s">
+      <c r="F10" s="1" t="s">
         <v>33</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -744,7 +753,27 @@
         <v>36</v>
       </c>
       <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>37</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
